--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_rep_QuestSweep.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_rep_QuestSweep.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12345"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_accumulateLogOn" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>扫荡id</t>
   </si>
@@ -96,61 +96,40 @@
     <t>80000301#2</t>
   </si>
   <si>
-    <t>80000401#1</t>
-  </si>
-  <si>
     <t>卡利玛神庙第2层</t>
   </si>
   <si>
     <t>80000202#1</t>
   </si>
   <si>
-    <t>80000402#1</t>
-  </si>
-  <si>
     <t>卡利玛神庙第3层</t>
   </si>
   <si>
     <t>80000203#1</t>
   </si>
   <si>
-    <t>80000403#1</t>
-  </si>
-  <si>
     <t>卡利玛神庙第4层</t>
   </si>
   <si>
     <t>80000204#1</t>
   </si>
   <si>
-    <t>80000404#1</t>
-  </si>
-  <si>
     <t>卡利玛神庙第5层</t>
   </si>
   <si>
     <t>80000205#1</t>
   </si>
   <si>
-    <t>80000405#1</t>
-  </si>
-  <si>
     <t>卡利玛神庙第6层</t>
   </si>
   <si>
     <t>80000206#1</t>
   </si>
   <si>
-    <t>80000406#1</t>
-  </si>
-  <si>
     <t>卡利玛神庙第7层</t>
   </si>
   <si>
     <t>80000207#1</t>
-  </si>
-  <si>
-    <t>80000407#1</t>
   </si>
 </sst>
 </file>
@@ -1206,25 +1185,19 @@
       <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="6" ht="15" spans="1:5">
       <c r="A6" s="3">
         <v>20002</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" ht="15" spans="1:5">
@@ -1232,16 +1205,13 @@
         <v>20003</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:5">
@@ -1249,16 +1219,13 @@
         <v>20004</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" ht="15" spans="1:5">
@@ -1266,16 +1233,13 @@
         <v>20005</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" ht="15" spans="1:5">
@@ -1283,16 +1247,13 @@
         <v>20006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:5">
@@ -1300,31 +1261,28 @@
         <v>20007</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="5:5">
+    </row>
+    <row r="12" ht="15" spans="1:5">
       <c r="E12" s="5"/>
     </row>
-    <row r="13" ht="15" spans="5:5">
+    <row r="13" ht="15" spans="1:5">
       <c r="E13" s="5"/>
     </row>
-    <row r="14" ht="15" spans="5:5">
+    <row r="14" ht="15" spans="1:5">
       <c r="E14" s="5"/>
     </row>
-    <row r="15" ht="15" spans="5:5">
+    <row r="15" ht="15" spans="1:5">
       <c r="E15" s="5"/>
     </row>
-    <row r="16" ht="15" spans="5:5">
+    <row r="16" ht="15" spans="1:5">
       <c r="E16" s="5"/>
     </row>
     <row r="17" ht="15" spans="5:5">
